--- a/envios/track2/A3_EMBS_ITBA_methods_description_form.xlsx
+++ b/envios/track2/A3_EMBS_ITBA_methods_description_form.xlsx
@@ -657,7 +657,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" style="7" min="1" max="1"/>
-    <col width="100" customWidth="1" style="7" min="2" max="2"/>
+    <col width="110" customWidth="1" style="7" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1" s="7">
@@ -704,12 +704,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>We went from genome to candidates in four stages, all scripted and reproducible with a single command (python run_pipeline.py).
-1. VARIANT. We filtered PASS variants from the proband's whole-genome VCF against a 321-gene panel covering mitosis, kinetochore, centrosome, cohesin, nuclear lamina and pore, chromatin, DNA repair and cell cycle. We kept rare variants (gnomAD v4 AF &lt; 1%) with a protein-altering consequence in the MANE Select transcript (Ensembl VEP), then looked for a recessive pattern (homozygous, or two heterozygous variants in the same gene). BUB1B was the only gene in the panel with two rare functional variants. We classified them with ACMG/AMP using the points system.
-2. MECHANISM. We characterised each allele separately (NMD prediction by the 50-55 nt rule; AlphaFold structure, residue burial and hydrogen bonding; ddG with ThermoMPNN) and converged on a single quantitative statement: this patient has too little BUBR1 protein rather than defective BUBR1 function. See Q10 for why that distinction drove every drug decision.
-3. THERAPEUTIC LINES. From the mechanism we derived four directions of action: raise BUBR1 protein level, inhibit mTORC1 (hyperactive in BubR1-low mice), clear senescent aneuploid cells, and treat the tumour without worsening aneuploidy. Each line specifies the direction of effect sought, so a drug can be judged against it.
-4. CANDIDATES. We built a long list of 86 drugs per line from DGIdb v5 and Open Targets plus a curated list with sources for what the databases miss. We then applied exclusion filters (approval verified directly in Drugs@FDA/openFDA and the EMA register, not in the interaction database) and a mechanism-based exclusion: any drug that would further weaken mitosis was removed, which ruled out all HSP90, PLK1, Aurora, MPS1 and APC/C inhibitors. Survivors were scored on six weighted criteria (mechanistic link 25, paediatric safety 20, evidence 15, case compatibility 15, innovation 15, feasible validation 10). Finally, every drug claim was checked against the primary paper and the FDA label, which changed two scores (see Q11).
-The proposal deliberately separates two things: the rhabdomyosarcoma is treated by the standard oncology protocol (reduced-intensity VAC, which includes cyclophosphamide and is not repurposing), while our contribution is a continuous regimen aimed at the underlying disease, which nothing currently treats: oral sirolimus, arimoclomol and niacin. We also report a pharmacogenomic analysis of the patient's CYP2B6, CYP2C19, CYP3A4, CYP3A5 and ABCB1 variants to inform dosing.</t>
+          <t>We went from genotype to mechanism to drugs in four steps, all scripted (single entry point: run_pipeline.py).
+1) Causal variant. Patient WGS VCF (GRCh38). PASS variants in a 321-gene panel (mitosis, kinetochore, centrosome, cohesin, nuclear envelope/pore, chromatin, DNA repair, cell cycle) were annotated with gnomAD v4 (rare: AF &lt; 1%), Ensembl VEP on the MANE Select transcript, CADD v1.7, ClinVar and dbNSFP predictors, filtered under a recessive model and classified with the ACMG/AMP points system. Funnel: 24,604 PASS variants -&gt; 14 rare protein-altering variants in MANE -&gt; one gene with two variants: BUB1B. A dominant model on 92 PanelApp genes looked for a second diagnosis.
+2) Mechanism. NMD prediction (50-55 nt rule), AlphaFold structure and residue environment, stability (ThermoMPNN ddG) and literature verified in PubMed -&gt; loss of function through a shortage of BUBR1 protein.
+3) Drug long list. From the mechanism we defined four therapeutic lines with the required direction of action: raise BUBR1 levels, dampen mTORC1, clear senescent cells, and treat the tumour without worsening aneuploidy. Candidates came from DGIdb v5, Open Targets and a curated list with sources (86 drugs). Exclusion filters: marketing approval checked in Drugs@FDA (openFDA) and EMA, and removal of drugs that weaken mitosis (HSP90, PLK1, Aurora, MPS1, APC/C inhibitors) -&gt; 73 drugs.
+4) Scoring and verification. Six weighted criteria scored 0-3 (mechanistic link 25, paediatric safety 20, evidence 15, fit to the case 15, innovation 15, feasible validation 10; 0-100 scale). Every claim was checked against the primary paper and the FDA label; this corrected two scores. Patient pharmacogenetics (CYP2B6, CYP2C19, CYP3A5, ABCB1) per CPIC/PharmGKB.
+Result: two parallel treatments. Cyclophosphamide continues as part of the treatment the patient already receives for the current rhabdomyosarcoma (standard care, not repurposing). For the remaining manifestations, we propose a long-term combination of oral sirolimus + arimoclomol + niacin, started alongside tumour treatment and maintained afterwards (niacin as an explicitly speculative hypothesis). Temsirolimus is kept for relapse, dasatinib for after chemotherapy, and a MEK inhibitor + temsirolimus only if the tumour shows RAS activation. All candidates can be tested in patient fibroblasts (BUBR1 Western blot, nocodazole mitotic-arrest assay).</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Four tools were used. Only the first received any patient-derived data.
-1. Anthropic Claude Code (Sonnet and Opus), Pro plan, consumer terms, 'Help improve Claude' disabled (no training on chats). Used for analysis code, API queries, literature verification and drafting. Received patient-derived output at variant level (positions, alleles, read depths); the VCF, raw reads and clinical document never left the local machine.
-2. Anthropic Claude (web application), free tier, training setting not confirmed by the user. Used only for literature search on the disease and its described treatments. No patient data.
-3. Google Gemini (gemini-3.5-flash-lite and gemini-3.8-flash) through the Gemini API with LangChain, UNPAID tier. Google's unpaid-tier terms state that submitted content and generated responses are used to 'provide, improve, and develop' their products and that 'human reviewers may read, annotate, and process your API input and output'. We note this explicitly because those same terms warn against submitting sensitive or personal information. No patient data was sent: the prompt contained only the disease name, the BUB1B gene and therapeutic target names (verifiable in notebooks/06). Its output was a first draft that was discarded; the final drug list comes from scripts/lista_larga_farmacos.py.
-4. Perplexity, free tier, training setting not confirmed by the user. Used only for literature search on the disease and its described treatments. No patient data.
-Every AI-generated claim was verified against the primary source. Claims that could not be verified were removed from the report.</t>
+          <t>• Claude Code (Sonnet and Opus), Anthropic, Claude Pro plan, consumer terms, "Help improve Claude" disabled (K. García).
+• Claude Code, Anthropic, Claude Pro plan, consumer terms, "Help improve Claude" disabled (L. Vargas).
+• Gemini 3.5-flash-lite and 3.8-flash (API through LangChain, notebook 06), Google, free tier of the API: content sent and responses may be used by Google to improve its products and may be read by human reviewers. Used by the team for an early draft of drug ideas, not used as the final list. Received only the disease name, the gene BUB1B, therapeutic target names and public database results; no patient data.
+• Claude (app), Anthropic, free plan; "Help improve Claude" setting not verified. Literature search on the disease and its treatments; no patient data.
+• Perplexity, Perplexity AI, free plan; data retention setting not verified. Literature search on the disease and its treatments; no patient data.
+All AI-generated statements were verified against primary sources (PubMed, Drugs@FDA, gnomAD, UniProt).</t>
         </is>
       </c>
     </row>
@@ -738,10 +738,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Both, in clearly separated roles.
-AUTOMATED: panel filtering and variant annotation (gnomAD v4, Ensembl VEP on MANE Select, ClinVar, CADD, dbNSFP predictors); long-list construction by querying DGIdb v5 and the Open Targets Platform per target; and approval checking against Drugs@FDA (openFDA) and the EMA centralised register. All scripted, cached and reproducible.
-MANUAL / EXPERT CURATION: the six-criterion scoring of each candidate; a curated drug list for mechanisms the databases do not capture; the biological review of whether each drug would worsen mitosis; and verification of every factual claim against the primary literature and the regulatory label. Detail in Q11.
-An LLM was used to draft code and text and to orient literature searches, but not as the source of the final candidate list. An early LLM-generated drug list (Gemini, notebooks/06) was discarded precisely because it could not be traced to verifiable sources.</t>
+          <t>Hybrid. Candidate generation was automated: scripts/lista_larga_farmacos.py queries DGIdb v5 and Open Targets and checks approval status in openFDA and the EMA database. The scoring criteria were defined by the team; scoring, the curated additions and the final selection were manual curation with AI assistance, reviewed by a team member, with every statement verified against the primary source.</t>
         </is>
       </c>
     </row>
@@ -753,12 +750,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Manual curation was the step that changed the result most, in four ways.
-1. CLAIM-BY-CLAIM VERIFICATION. Every statement about a drug was checked against the original paper in PubMed and against the FDA label. This corrected two scores. Sirolimus dropped from 80 to 71.7 because the paper we had cited (Sieben 2020, PMID 31738183) only ASSOCIATES sarcopenia with hyperactive mTORC1 in BubR1-mutant mice; it did not treat them with rapamycin. The rapamycin treatment result is in wild-type mice (Ham 2020, PMID 32908143). Arimoclomol dropped from 73.3 to 68.3 after reading the FDA label, which states that its mechanism in Niemann-Pick C is unknown and warns about weight loss and renal findings, both relevant in a child with failure to thrive and nephrocalcinosis. Citations that could not be verified in PubMed were deleted.
-2. MECHANISM-BASED EXCLUSION. We asked of each candidate whether, beyond its intended effect, it would further weaken cell division in a patient whose spindle assembly checkpoint is already compromised. This excluded HSP90, PLK1, Aurora, MPS1 and APC/C inhibitors as a class, and flagged bortezomib: by blocking the proteasome it also blocks cyclin B and securin degradation, delaying mitotic exit, and adds neuropathy on top of vincristine. It was removed from the short list.
-3. REVERSED JUDGEMENTS AFTER CHALLENGE. When a team member argued for nab-sirolimus on tumour-accumulation grounds, we re-examined it and found our own write-up was wrong: a Children's Oncology Group phase 1 with a defined paediatric MTD does exist (PMID 39487711), and tumour accumulation is measured in xenografts. We corrected the document and reclassified the drug rather than defending the earlier position.
-4. COMPOUND DISAMBIGUATION. Our NAD+/SIRT2 hypothesis requires niacin (nicotinic acid), not nicotinamide, even though both are vitamin B3 and are often used interchangeably. Nicotinamide is the product of the sirtuin reaction and its feedback inhibitor, whereas nicotinic acid had no effect on SIRT1 in the same study (PMID 12297502). Proposing the inhibitor of the enzyme the hypothesis depends on would have been self-defeating.
-We also ran a dominant-model analysis over 92 PanelApp green genes looking for a second diagnosis, which found an incidental LZTR1 truncating variant, and extended it to 10 genes proposed by the team (including BRCA1/2, PALB2, RAD51C/D, CHEK2), all negative.</t>
+          <t>• Curated list (config/lineas_terapeuticas.json) for mechanisms the databases do not capture (e.g. arimoclomol, phenylbutyrate, rapalogs, dasatinib), each with its source.
+• Scoring criteria and 0-3 scales defined by the team from the literature and the challenge's evaluation criteria. The 55 candidates were scored with AI assistance, each with a written justification and sources (results/candidatos_farmacos.tsv), and the scores were reviewed by a team member (L. Ogas). Niacin and two MEK inhibitors (conditional on RAS activation in the tumour) were added by hand.
+• Biological safety review: for each candidate we asked whether it further weakens mitosis in a patient with a weak checkpoint. This removed bortezomib (delays mitotic exit, adds neuropathy with vincristine).
+• Verification against the original paper and FDA label corrected sirolimus (a cited study associated, but did not treat, BubR1 mice) and arimoclomol (label states mechanism unknown; renal and weight warnings).
+• Niacin vs nicotinamide: nicotinamide inhibits sirtuins (PMID 12297502), so only niacin fits the SIRT2-BubR1 hypothesis.
+• All references were cross-checked against PubMed (E-utilities).</t>
         </is>
       </c>
     </row>
@@ -770,8 +767,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Solely publicly available databases and literature. No external proprietary data source was used.
-The only access-controlled input is the challenge's own dataset (SageBio/mva-hackathon-2026-data on Hugging Face): the proband's VCF and clinical document, used under the challenge access terms. That is the subject of the analysis, not an external proprietary source. Those files were never uploaded to the repository, shared outside the team, or sent to any third-party service.</t>
+          <t>Only publicly available databases and literature. The patient genome and clinical summary come from the challenge dataset (SageBio/mva-hackathon-2026-data).</t>
         </is>
       </c>
     </row>
@@ -783,10 +779,9 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>VARIANT AND GENE: gnomAD v4 (allele frequencies and gene constraint, LOEUF/pLI), Ensembl VEP with MANE Select transcripts, ClinVar, CADD v1.7, dbNSFP predictors (including REVEL), myvariant.info, UniProt (O60566, BUBR1), and PanelApp from Genomics England for the dominant-model gene panels (nephrocalcinosis, renal tubulopathies, calcium/parathyroid, CASR, familial rhabdomyosarcoma, childhood solid tumours, sarcoma susceptibility, monogenic short stature).
-STRUCTURE AND STABILITY: AlphaFold and AlphaFill models, and ThermoMPNN for ddG predictions across the pseudokinase domain.
-DRUGS AND TARGETS: DGIdb v5 and the Open Targets Platform for drug-target relationships and rhabdomyosarcoma trial links; Drugs@FDA via openFDA and the EMA register of centrally authorised medicines for approval status and label text; CPIC and PharmGKB for pharmacogenomic phenotype assignment.
-LITERATURE: PubMed, with every citation checked for existence and content. Key sources include Hanks 2004 (PMID 15475955, founding BUB1B-MVA paper), Suijkerbuijk 2010 (PMID 20516114, pseudokinase missense variants reduce BUBR1 protein level), Sieben 2020 (PMID 31738183), Mascarenhas 2019 (PMID 31513481, temsirolimus phase II in relapsed rhabdomyosarcoma), Defachelles 2021 (PMID 34343032, VIT-0910), Hol 2021 (PMID 34134020, SIOP-Europe Wilms tumour surveillance) and Nakano 2024 (PMID 39264246).</t>
+          <t>Drugs and targets: DGIdb v5, Open Targets Platform (including rhabdomyosarcoma trials), Drugs@FDA via openFDA, EMA medicines database, FDA labels, CPIC and PharmGKB.
+Variants and genes: gnomAD v4, ClinVar, Ensembl VEP (MANE Select), CADD v1.7, dbNSFP via myvariant.info, ClinGen, PanelApp, UniProt, AlphaFold DB, AlphaFill.
+Literature: PubMed, every citation verified (e.g. Suijkerbuijk 2010 PMID 20516114; Sieben 2020 PMID 31738183; North 2014 PMID 24825348; Mascarenhas 2019 PMID 31513481; Nishitani-Isa 2019 PMID 31184400).</t>
         </is>
       </c>
     </row>
@@ -810,12 +805,11 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>LOSS OF FUNCTION, and specifically loss of protein QUANTITY rather than of catalytic activity. That distinction is the core of our proposal, because it changes which targets are worth pursuing.
-GENOTYPE: compound heterozygous BUB1B. Allele 1, p.Leu737Ter, is a premature stop in exon 17 of 23, more than 55 nt from the last exon-exon junction, so NMD is predicted by the 50-55 nt rule and the allele is expected to produce no protein (classified likely pathogenic, 9 points; pathogenic in ClinVar). Allele 2, p.Asn1002Lys, is a missense in the pseudokinase domain: a buried residue (pLDDT 91) making three hydrogen bonds that lysine cannot form, with ddG +1.5 kcal/mol (72nd-75th percentile of the domain), about half that of the known MVA variant p.Leu1012Pro (+3.1). It does not contact the ATP pocket (29 A away). It remains a VUS leaning pathogenic.
-WHY QUANTITY AND NOT FUNCTION: every MVA missense variant in this domain characterised in cells reduces BUBR1 abundance five- to ten-fold through misfolding, and restoring normal levels restores checkpoint function (Suijkerbuijk 2010, PMID 20516114). So a null allele plus a destabilised hypomorphic allele converge on the same endpoint: too little BUBR1.
-PATHWAY DISRUPTED: the spindle assembly checkpoint (SAC). BUBR1 is a core component of the mitotic checkpoint complex that inhibits the APC/C until all chromosomes are properly attached.
-DOWNSTREAM CONSEQUENCE: a weak checkpoint allows chromosome missegregation, producing mosaic aneuploidy, which branches into (a) senescence and premature ageing, with hyperactive mTORC1 described in BubR1-low mice, matching the growth restriction, short stature and muscle atrophy, and (b) chromosomal instability, matching the rhabdomyosarcoma. The nephrocalcinosis is not explained by this mechanism and we say so: no renal gene accounted for it under either dominant or recessive models, and prematurity is the more likely cause (PMID 38296790).
-A clinically relevant corollary we did not find discussed in the MVA literature: vincristine, present in every rhabdomyosarcoma protocol, kills through SAC-dependent mitotic arrest, which is precisely what is impaired here. BubR1-haploinsufficient mice show mitotic slippage (PMID 14744753), but the published evidence runs in both directions (PMID 17172401), so we raise it as an open question with a concrete experiment rather than as a claim.</t>
+          <t>BUB1B compound heterozygote. Allele 1, c.2210T&gt;G p.Leu737Ter: premature stop in exon 17 of 23, predicted NMD (null allele; ClinVar pathogenic; ACMG likely pathogenic). Allele 2, c.3006T&gt;G p.Asn1002Lys: missense in the pseudokinase domain, ACMG VUS leaning pathogenic. Buried residue (pLDDT 91) losing 3 hydrogen bonds; ThermoMPNN ddG +1.5 kcal/mol (predicted destabilising, half of the known MVA variant p.Leu1012Pro), far from the ATP pocket. In cells, all MVA missense variants studied in this domain lower BUBR1 5-10 fold by misfolding, and restoring the amount rescues the checkpoint (Suijkerbuijk 2010).
+Effect: partial loss of function through a shortage of BUBR1 protein, not loss of catalytic activity.
+Pathway: spindle assembly checkpoint (SAC); BUBR1 is a core component of the mitotic checkpoint complex.
+Consequence: weak checkpoint -&gt; chromosome mis-segregation -&gt; mosaic aneuploidy -&gt; (a) senescence/premature ageing with hyperactive mTORC1 in BubR1 mice (growth restriction, muscle atrophy) and (b) chromosomal instability (rhabdomyosarcoma).
+Limitations: phase (trans) not proven, no parental samples; allele 2 is a VUS without functional data.</t>
         </is>
       </c>
     </row>
@@ -827,8 +821,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Approximately 120 person-hours across five weeks (17 September to 24 October 2026).
-Per-person hours were not logged, so this is an estimate derived from the repository record rather than a time sheet: 104 commits over 11 active days, 2,254 lines of Python across 13 analysis scripts, eight report sections, and a dated work log in docs/bitacora.md. Effort was concentrated unevenly: one contributor accounts for roughly 85% of commits (all of the computational work and the report), with four others contributing domain review, the gene list and documentation. A substantial share of the total went not to writing code but to verifying AI-generated claims against primary sources, which is what produced the corrections described in Q11.</t>
+          <t>Five team members over five weeks (17 Sep - 24 Oct 2026), about 8 hours per person per week: approximately 200 person-hours. Full pipeline re-run: 6 min 11 s with cached API queries (Windows 11, Python 3.13); a clean run without the cache takes considerably longer (about 35,000 variants annotated through public APIs).</t>
         </is>
       </c>
     </row>
@@ -840,11 +833,11 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>BACKGROUND. Mosaic variegated aneuploidy (MVA) is an ultra-rare paediatric chromosome instability syndrome with no disease-modifying treatment. We analysed a proband with rhabdomyosarcoma, nephrocalcinosis, severe intrauterine growth restriction and short stature.
-METHODS. From the whole-genome VCF we filtered PASS variants across a 321-gene mitosis and genome-stability panel, retaining rare variants (gnomAD v4 AF &lt; 1%) with a protein-altering consequence in the MANE Select transcript, and tested for recessive patterns. BUB1B was the only gene with two rare functional variants. We characterised each allele (NMD by the 50-55 nt rule; AlphaFold burial and hydrogen bonding; ThermoMPNN ddG), derived four mechanism-based therapeutic directions, built an 86-drug long list from DGIdb v5, Open Targets and a sourced curated list, verified approval directly in Drugs@FDA and the EMA register, excluded drugs that would further weaken mitosis, and scored survivors on six weighted criteria. We additionally ran a dominant model over 92 PanelApp genes to test for a second diagnosis, and a pharmacogenomic analysis of CYP2B6, CYP2C19, CYP3A4, CYP3A5 and ABCB1.
-RESULTS. Compound heterozygous BUB1B: p.Leu737Ter (null, NMD predicted) and p.Asn1002Lys (destabilising pseudokinase missense, ddG +1.5 kcal/mol). Both converge on reduced BUBR1 ABUNDANCE rather than impaired activity, which reframes MVA as a protein-quantity disease and redirects the target space. Our proposal separates standard oncology (reduced-intensity VAC, including cyclophosphamide, which is not repurposing) from a continuous regimen for the untreated underlying disease: oral sirolimus (mTORC1), arimoclomol (proteostasis) and niacin (NAD+/SIRT2-mediated BubR1 stabilisation; explicitly speculative). The dominant model additionally identified an incidental LZTR1 truncating variant, likely pathogenic for LZTR1-related schwannomatosis, which carries actionable paediatric surveillance guidance.
-STRENGTHS. The pipeline is reproducible with one command and uses only public APIs; the reference run completed all eight steps in 6 min 11 s and reproduced every number in the report. Every drug claim was verified against the primary paper and the regulatory label, which corrected two of our own scores and reversed one judgement. Mechanistic reasoning was applied as an exclusion criterion, not only a selection one. We report the highest clinical-impact finding even though it is not a drug: Wilms tumour risk in BUB1B-MVA is approximately 50%, and the recommended three-monthly renal ultrasound is already indicated for this patient's nephrocalcinosis, so surveillance adds no cost.
-LIMITATIONS. Trans phase cannot be established without parental samples and is not resolvable from this dataset. Allele 2 remains a VUS. No candidate has been tested in MVA; evidence is preclinical or from other diseases, and arimoclomol's own FDA label states its mechanism is unknown. Structural and non-coding variants were not assessed. The nephrocalcinosis is unexplained. The niacin hypothesis rests on a single unreplicated mouse result obtained with a different NAD+ precursor. All candidates are falsifiable in one inexpensive experiment: patient fibroblasts before and after treatment, measuring BUBR1 by Western blot and checkpoint response with nocodazole.</t>
+          <t>We present a reproducible path from a patient's whole genome to repurposable approved drugs for mosaic variegated aneuploidy (MVA). Starting from the PASS variants of the patient VCF, we screened a 321-gene panel of mitosis, kinetochore, cohesin, chromatin and DNA-repair genes with population frequency (gnomAD v4), consequence on the MANE Select transcript (Ensembl VEP), in-silico predictors and ACMG/AMP points. Of 24,604 PASS variants, BUB1B was the only gene carrying two rare protein-altering variants: p.Leu737Ter (predicted NMD, null allele) and p.Asn1002Lys (pseudokinase missense, VUS leaning pathogenic). Using MANE annotation removed five false alerts that were severe only on secondary transcripts.
+Mechanism: structural modelling (AlphaFold, ThermoMPNN) predicts that p.Asn1002Lys destabilises BUBR1, and published cell work shows that missense variants in this domain lower BUBR1 levels and that restoring the amount restores the spindle assembly checkpoint. We therefore frame this case as a quantitative protein deficiency: partial loss of function leading to a weak checkpoint, mosaic aneuploidy, premature ageing with hyperactive mTORC1, and rhabdomyosarcoma.
+Drug repurposing: we derived four therapeutic lines with an explicit direction of action, assembled 86 candidates from DGIdb, Open Targets and a curated list, kept only drugs with verified FDA or EMA approval, and excluded every drug that weakens mitosis. Candidates were scored on six weighted criteria and every claim was checked against the primary paper and FDA label. The proposal separates two treatments: cyclophosphamide continues as part of the treatment the patient already receives for the current rhabdomyosarcoma, and, for the remaining manifestations that no current therapy addresses, we propose a long-term combination of oral sirolimus (mTORC1), arimoclomol (protein folding, to raise BUBR1) and niacin (NAD+-SIRT2-BubR1 axis, an explicitly speculative hypothesis), which could also indirectly lower the risk of new tumours. Patient pharmacogenetics (CYP2B6 intermediate metaboliser) is consistent with reduced cyclophosphamide intensity. A dominant-model search found a secondary finding in LZTR1 (schwannomatosis predisposition) that warrants surveillance. The mechanism also predicts that antimitotic chemotherapy may behave differently with a weak checkpoint.
+Strengths: a fully scripted pipeline (one command, about 6 minutes with cache), public data only, MANE-aware annotation, mechanism-driven filters that exclude harmful drugs, verified references, and a single low-cost validation experiment shared by all candidates (BUBR1 Western blot and nocodazole arrest in patient fibroblasts).
+Limitations: no parental samples, so the trans phase is assumed, not proven; allele 2 is a VUS without functional data; none of the candidates has been tested in MVA, and the niacin hypothesis rests on mouse data with NMN that lacks independent replication; arimoclomol's mechanism is officially unknown; the pipeline has been run end-to-end only on Windows and has no automated tests.</t>
         </is>
       </c>
     </row>

--- a/envios/track2/A3_EMBS_ITBA_methods_description_form.xlsx
+++ b/envios/track2/A3_EMBS_ITBA_methods_description_form.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Five team members over five weeks (17 Sep - 24 Oct 2026), about 8 hours per person per week: approximately 200 person-hours. Full pipeline re-run: 6 min 11 s with cached API queries (Windows 11, Python 3.13); a clean run without the cache takes considerably longer (about 35,000 variants annotated through public APIs).</t>
+          <t>Five team members over five weeks (17 Sep - 24 Oct 2026): approximately 42 person-hours in total (K. García 10, L. Vargas 10, J. Wohlfeiler 8, L. Ogas 8, T. German 6). Full pipeline re-run: 6 min 11 s with cached API queries (Windows 11, Python 3.13); a clean run without the cache takes considerably longer (about 35,000 variants annotated through public APIs).</t>
         </is>
       </c>
     </row>

--- a/envios/track2/A3_EMBS_ITBA_methods_description_form.xlsx
+++ b/envios/track2/A3_EMBS_ITBA_methods_description_form.xlsx
@@ -6,8 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="27480" yWindow="15680" windowWidth="42340" windowHeight="26880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Track 1 methods" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Track 2 methods" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Track 2 methods" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -198,22 +197,6 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>MVA Hackathon Organizers</author>
-  </authors>
-  <commentList>
-    <comment ref="B7" authorId="0" shapeId="0">
-      <text>
-        <t>Yellow cells are for your answers.
-Example: "HelixSquad"</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -503,156 +486,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col width="85.1640625" customWidth="1" style="7" min="1" max="1"/>
-    <col width="45" customWidth="1" style="7" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="16" customHeight="1" s="7">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Methods description — MVA Hackathon 2026, Track 1 (Variant Prediction)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="70" customHeight="1" s="7">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Please submit your answers with your Track 1 submission. All questions (with the exception of Question 1, in red) are voluntary; however, submissions without a methods description may be judged less favorably on the Innovation and Scalability criteria, since the panel can't assess what it can't see.
-Fill out this form once per model/approach submitted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="6" ht="16" customHeight="1" s="7">
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Answers</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Team name</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Model number (fill out this form once per model/approach submitted; up to 6)</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Please describe your model/approach in detail.</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n"/>
-    </row>
-    <row r="10" ht="45" customHeight="1" s="7">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>(required) If commercially-available Generative AI was used, record the provider, the plan or tier, and the relevant setting in your methods description. A line is enough, for example, "Anthropic API, Claude Sonnet, commercial terms, no training on customer content."</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1" s="7">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Please state whether the submission file is the automated output of your computational approach (preferred), or if it has undergone downstream manual review and curation.</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Please describe any downstream manual review in detail.</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13" ht="45" customHeight="1" s="7">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Please state whether your approach only used publicly available data (preferred) or if proprietary data was also used. If proprietary data were used, where possible, please also include a submission based only on publicly available data.</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14" ht="30" customHeight="1" s="7">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Please describe any public data used in detail (e.g., reference panels, population databases, literature).</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Please describe any proprietary data used in detail.</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-    </row>
-    <row r="16" ht="30" customHeight="1" s="7">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Is your approach able to output proposed pairs of compound heterozygous candidate variants, or only single candidate variants?</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1" s="7">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>How did you handle secondary or incidental findings, if any? (See the finding_type column in your submission.)</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Please provide an estimate of run time and cost for your approach (if possible).</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1" s="7">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Provide a method abstract (up to 500 words). Please include strengths and limitations of your method as well as methodological detail.</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:B4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
